--- a/Models/Верблюды/results/Верблюды - лучшие модели.xlsx
+++ b/Models/Верблюды/results/Верблюды - лучшие модели.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>4.491418702812721e+17</v>
+        <v>2.342988110753842e+17</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="C3" t="n">
-        <v>4.9</v>
+        <v>2.34</v>
       </c>
       <c r="D3" t="n">
-        <v>9.01</v>
+        <v>11.96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -500,17 +500,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.73</v>
+        <v>86.55</v>
       </c>
       <c r="C4" t="n">
-        <v>64.91</v>
+        <v>88.69</v>
       </c>
       <c r="D4" t="n">
-        <v>328.09</v>
+        <v>326.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.05</v>
+        <v>13.84</v>
       </c>
       <c r="C5" t="n">
-        <v>14.69</v>
+        <v>16.87</v>
       </c>
       <c r="D5" t="n">
-        <v>24.34</v>
+        <v>28.43</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.58495566170773e+21</v>
+        <v>4.481981798858405e+21</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>13.33</v>
+        <v>0</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.039999999999999</v>
+        <v>7.23</v>
       </c>
       <c r="C10" t="n">
-        <v>8.92</v>
+        <v>7.06</v>
       </c>
       <c r="D10" t="n">
-        <v>35.17</v>
+        <v>39.58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.07</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>24.7</v>
+        <v>22.82</v>
       </c>
       <c r="D11" t="n">
-        <v>50.79</v>
+        <v>47.04</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.563890366910331e+23</v>
+        <v>3.268766828792398e+23</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>3.980634468878198e+19</v>
+        <v>3.587249808869536e+19</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>192.84</v>
+        <v>44.56</v>
       </c>
       <c r="C14" t="n">
-        <v>225.74</v>
+        <v>46.28</v>
       </c>
       <c r="D14" t="n">
-        <v>1073.73</v>
+        <v>306.88</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,17 +707,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24.7</v>
+        <v>32.34</v>
       </c>
       <c r="C15" t="n">
-        <v>21.15</v>
+        <v>43.24</v>
       </c>
       <c r="D15" t="n">
-        <v>29.31</v>
+        <v>33.17</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>4.283582583501973e+18</v>
+        <v>3.075002658089149e+21</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>1.848497784684796e+21</v>
+        <v>3.031759413706881e+17</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>1.00953810947756e+17</v>
+        <v>15</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>3.105163200541414e+18</v>
+        <v>4.87848243235304e+18</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>9.555317582725239e+18</v>
+        <v>3.116639736815847e+18</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
@@ -813,17 +813,17 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.85</v>
+        <v>20.88</v>
       </c>
       <c r="C21" t="n">
-        <v>17.7</v>
+        <v>23.49</v>
       </c>
       <c r="D21" t="n">
-        <v>23.38</v>
+        <v>17.35</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>Prophet</t>
         </is>
       </c>
     </row>
